--- a/output/yearly_population_iteration_59_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_59_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7171</v>
+        <v>5992</v>
       </c>
       <c r="C2" t="n">
-        <v>15631</v>
+        <v>9627</v>
       </c>
       <c r="D2" t="n">
-        <v>26792</v>
+        <v>21086</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3559</v>
+        <v>3486</v>
       </c>
       <c r="C3" t="n">
-        <v>7679</v>
+        <v>4657</v>
       </c>
       <c r="D3" t="n">
-        <v>12589</v>
+        <v>14524</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3005</v>
+        <v>2655</v>
       </c>
       <c r="C4" t="n">
-        <v>4560</v>
+        <v>4288</v>
       </c>
       <c r="D4" t="n">
-        <v>6348</v>
+        <v>6776</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2003</v>
+        <v>1754</v>
       </c>
       <c r="C5" t="n">
-        <v>4592</v>
+        <v>3883</v>
       </c>
       <c r="D5" t="n">
-        <v>2543</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1125</v>
+        <v>1074</v>
       </c>
       <c r="C6" t="n">
-        <v>3940</v>
+        <v>2486</v>
       </c>
       <c r="D6" t="n">
-        <v>1141</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="C7" t="n">
-        <v>2712</v>
+        <v>1404</v>
       </c>
       <c r="D7" t="n">
-        <v>650</v>
+        <v>636</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="C8" t="n">
-        <v>1352</v>
+        <v>761</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>506</v>
+        <v>368</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7794</v>
+        <v>7508</v>
       </c>
       <c r="C2" t="n">
-        <v>20764</v>
+        <v>7404</v>
       </c>
       <c r="D2" t="n">
-        <v>23329</v>
+        <v>25495</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4144</v>
+        <v>3754</v>
       </c>
       <c r="C3" t="n">
-        <v>9784</v>
+        <v>6150</v>
       </c>
       <c r="D3" t="n">
-        <v>13581</v>
+        <v>14469</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2769</v>
+        <v>2589</v>
       </c>
       <c r="C4" t="n">
-        <v>5828</v>
+        <v>4383</v>
       </c>
       <c r="D4" t="n">
-        <v>7052</v>
+        <v>7908</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2138</v>
+        <v>1922</v>
       </c>
       <c r="C5" t="n">
-        <v>4438</v>
+        <v>3959</v>
       </c>
       <c r="D5" t="n">
-        <v>3050</v>
+        <v>2979</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1350</v>
+        <v>1253</v>
       </c>
       <c r="C6" t="n">
-        <v>4184</v>
+        <v>3117</v>
       </c>
       <c r="D6" t="n">
-        <v>1316</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C7" t="n">
-        <v>3201</v>
+        <v>1888</v>
       </c>
       <c r="D7" t="n">
-        <v>715</v>
+        <v>692</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="C8" t="n">
-        <v>1911</v>
+        <v>1050</v>
       </c>
       <c r="D8" t="n">
-        <v>449</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C9" t="n">
-        <v>832</v>
+        <v>533</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>334</v>
+        <v>281</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8590</v>
+        <v>9130</v>
       </c>
       <c r="C2" t="n">
-        <v>17700</v>
+        <v>7296</v>
       </c>
       <c r="D2" t="n">
-        <v>21120</v>
+        <v>30910</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4504</v>
+        <v>4321</v>
       </c>
       <c r="C3" t="n">
-        <v>12496</v>
+        <v>5972</v>
       </c>
       <c r="D3" t="n">
-        <v>13881</v>
+        <v>14931</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2804</v>
+        <v>2646</v>
       </c>
       <c r="C4" t="n">
-        <v>7283</v>
+        <v>5047</v>
       </c>
       <c r="D4" t="n">
-        <v>7777</v>
+        <v>8599</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2149</v>
+        <v>1957</v>
       </c>
       <c r="C5" t="n">
-        <v>4906</v>
+        <v>4025</v>
       </c>
       <c r="D5" t="n">
-        <v>3465</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1500</v>
+        <v>1398</v>
       </c>
       <c r="C6" t="n">
-        <v>4205</v>
+        <v>3451</v>
       </c>
       <c r="D6" t="n">
-        <v>1531</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="C7" t="n">
-        <v>3544</v>
+        <v>2386</v>
       </c>
       <c r="D7" t="n">
-        <v>777</v>
+        <v>765</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="C8" t="n">
-        <v>2390</v>
+        <v>1394</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="C9" t="n">
-        <v>1204</v>
+        <v>730</v>
       </c>
       <c r="D9" t="n">
-        <v>326</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C10" t="n">
-        <v>501</v>
+        <v>374</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7954</v>
+        <v>8197</v>
       </c>
       <c r="C2" t="n">
-        <v>12460</v>
+        <v>4844</v>
       </c>
       <c r="D2" t="n">
-        <v>17562</v>
+        <v>25054</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5151</v>
+        <v>5052</v>
       </c>
       <c r="C3" t="n">
-        <v>16841</v>
+        <v>8711</v>
       </c>
       <c r="D3" t="n">
-        <v>15123</v>
+        <v>16566</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1985</v>
+        <v>1808</v>
       </c>
       <c r="C4" t="n">
-        <v>8555</v>
+        <v>6722</v>
       </c>
       <c r="D4" t="n">
-        <v>7430</v>
+        <v>8180</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1386</v>
+        <v>1291</v>
       </c>
       <c r="C5" t="n">
-        <v>4120</v>
+        <v>3381</v>
       </c>
       <c r="D5" t="n">
-        <v>2398</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="C6" t="n">
-        <v>3473</v>
+        <v>2338</v>
       </c>
       <c r="D6" t="n">
-        <v>761</v>
+        <v>749</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>338</v>
+        <v>369</v>
       </c>
       <c r="C7" t="n">
-        <v>2342</v>
+        <v>1366</v>
       </c>
       <c r="D7" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="C8" t="n">
-        <v>1179</v>
+        <v>715</v>
       </c>
       <c r="D8" t="n">
-        <v>319</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>490</v>
+        <v>366</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4789</v>
+        <v>4935</v>
       </c>
       <c r="C2" t="n">
-        <v>6316</v>
+        <v>2874</v>
       </c>
       <c r="D2" t="n">
-        <v>12652</v>
+        <v>17348</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5402</v>
+        <v>5508</v>
       </c>
       <c r="C3" t="n">
-        <v>13614</v>
+        <v>6235</v>
       </c>
       <c r="D3" t="n">
-        <v>14588</v>
+        <v>16966</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2706</v>
+        <v>2689</v>
       </c>
       <c r="C4" t="n">
-        <v>12364</v>
+        <v>7795</v>
       </c>
       <c r="D4" t="n">
-        <v>8454</v>
+        <v>9376</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1515</v>
+        <v>1414</v>
       </c>
       <c r="C5" t="n">
-        <v>5895</v>
+        <v>4884</v>
       </c>
       <c r="D5" t="n">
-        <v>2950</v>
+        <v>3134</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>902</v>
+        <v>916</v>
       </c>
       <c r="C6" t="n">
-        <v>3897</v>
+        <v>2827</v>
       </c>
       <c r="D6" t="n">
-        <v>915</v>
+        <v>924</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>312</v>
+        <v>350</v>
       </c>
       <c r="C7" t="n">
-        <v>2801</v>
+        <v>1762</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="C8" t="n">
-        <v>1531</v>
+        <v>928</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>514</v>
+        <v>429</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5265</v>
+        <v>5382</v>
       </c>
       <c r="C2" t="n">
-        <v>5570</v>
+        <v>6520</v>
       </c>
       <c r="D2" t="n">
-        <v>11297</v>
+        <v>17148</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4340</v>
+        <v>4412</v>
       </c>
       <c r="C3" t="n">
-        <v>9271</v>
+        <v>4054</v>
       </c>
       <c r="D3" t="n">
-        <v>13484</v>
+        <v>15853</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3247</v>
+        <v>3392</v>
       </c>
       <c r="C4" t="n">
-        <v>12682</v>
+        <v>6839</v>
       </c>
       <c r="D4" t="n">
-        <v>9139</v>
+        <v>10402</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1776</v>
+        <v>1739</v>
       </c>
       <c r="C5" t="n">
-        <v>8629</v>
+        <v>6254</v>
       </c>
       <c r="D5" t="n">
-        <v>3624</v>
+        <v>4057</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1059</v>
+        <v>1042</v>
       </c>
       <c r="C6" t="n">
-        <v>4705</v>
+        <v>3746</v>
       </c>
       <c r="D6" t="n">
-        <v>1195</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>460</v>
+        <v>514</v>
       </c>
       <c r="C7" t="n">
-        <v>3278</v>
+        <v>2258</v>
       </c>
       <c r="D7" t="n">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="C8" t="n">
-        <v>2030</v>
+        <v>1288</v>
       </c>
       <c r="D8" t="n">
-        <v>343</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C9" t="n">
-        <v>877</v>
+        <v>632</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>331</v>
+        <v>304</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3223</v>
+        <v>3158</v>
       </c>
       <c r="C2" t="n">
-        <v>2749</v>
+        <v>2948</v>
       </c>
       <c r="D2" t="n">
-        <v>8007</v>
+        <v>11810</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4386</v>
+        <v>4486</v>
       </c>
       <c r="C3" t="n">
-        <v>7878</v>
+        <v>4785</v>
       </c>
       <c r="D3" t="n">
-        <v>12993</v>
+        <v>15617</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3550</v>
+        <v>3759</v>
       </c>
       <c r="C4" t="n">
-        <v>12620</v>
+        <v>6390</v>
       </c>
       <c r="D4" t="n">
-        <v>9703</v>
+        <v>11108</v>
       </c>
     </row>
     <row r="5">
@@ -2691,10 +2691,10 @@
         <v>1831</v>
       </c>
       <c r="C5" t="n">
-        <v>10717</v>
+        <v>7306</v>
       </c>
       <c r="D5" t="n">
-        <v>3725</v>
+        <v>4416</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>836</v>
+        <v>908</v>
       </c>
       <c r="C6" t="n">
-        <v>5614</v>
+        <v>4630</v>
       </c>
       <c r="D6" t="n">
-        <v>1174</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="C7" t="n">
-        <v>3500</v>
+        <v>2372</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>1436</v>
+        <v>1035</v>
       </c>
       <c r="D8" t="n">
-        <v>365</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>324</v>
+        <v>297</v>
       </c>
       <c r="D9" t="n">
-        <v>278</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="D11" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3117</v>
+        <v>4860</v>
       </c>
       <c r="C2" t="n">
-        <v>6375</v>
+        <v>8383</v>
       </c>
       <c r="D2" t="n">
-        <v>13543</v>
+        <v>12527</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3359</v>
+        <v>3316</v>
       </c>
       <c r="C3" t="n">
-        <v>5117</v>
+        <v>3477</v>
       </c>
       <c r="D3" t="n">
-        <v>11502</v>
+        <v>14144</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3409</v>
+        <v>3584</v>
       </c>
       <c r="C4" t="n">
-        <v>10263</v>
+        <v>5532</v>
       </c>
       <c r="D4" t="n">
-        <v>10006</v>
+        <v>11506</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2199</v>
+        <v>2318</v>
       </c>
       <c r="C5" t="n">
-        <v>11400</v>
+        <v>6802</v>
       </c>
       <c r="D5" t="n">
-        <v>4415</v>
+        <v>5309</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1069</v>
+        <v>1162</v>
       </c>
       <c r="C6" t="n">
-        <v>7629</v>
+        <v>5787</v>
       </c>
       <c r="D6" t="n">
-        <v>1477</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>297</v>
+        <v>351</v>
       </c>
       <c r="C7" t="n">
-        <v>4354</v>
+        <v>3346</v>
       </c>
       <c r="D7" t="n">
-        <v>632</v>
+        <v>651</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>2151</v>
+        <v>1552</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>657</v>
+        <v>551</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>38</v>
+      </c>
+      <c r="D15" t="n">
         <v>35</v>
-      </c>
-      <c r="D15" t="n">
-        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2225</v>
+        <v>3153</v>
       </c>
       <c r="C2" t="n">
-        <v>4021</v>
+        <v>4135</v>
       </c>
       <c r="D2" t="n">
-        <v>10155</v>
+        <v>9833</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2887</v>
+        <v>3359</v>
       </c>
       <c r="C3" t="n">
-        <v>5138</v>
+        <v>4954</v>
       </c>
       <c r="D3" t="n">
-        <v>11123</v>
+        <v>13180</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3096</v>
+        <v>3224</v>
       </c>
       <c r="C4" t="n">
-        <v>8418</v>
+        <v>4708</v>
       </c>
       <c r="D4" t="n">
-        <v>10080</v>
+        <v>11621</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2409</v>
+        <v>2574</v>
       </c>
       <c r="C5" t="n">
-        <v>11120</v>
+        <v>6446</v>
       </c>
       <c r="D5" t="n">
-        <v>4859</v>
+        <v>5963</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1218</v>
+        <v>1374</v>
       </c>
       <c r="C6" t="n">
-        <v>9005</v>
+        <v>6351</v>
       </c>
       <c r="D6" t="n">
-        <v>1714</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>263</v>
+        <v>341</v>
       </c>
       <c r="C7" t="n">
-        <v>5357</v>
+        <v>4196</v>
       </c>
       <c r="D7" t="n">
-        <v>706</v>
+        <v>732</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>2665</v>
+        <v>2003</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>693</v>
+        <v>659</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3436</v>
+        <v>5318</v>
       </c>
       <c r="C2" t="n">
-        <v>16164</v>
+        <v>13454</v>
       </c>
       <c r="D2" t="n">
-        <v>9694</v>
+        <v>13021</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2253</v>
+        <v>2761</v>
       </c>
       <c r="C3" t="n">
-        <v>4229</v>
+        <v>4089</v>
       </c>
       <c r="D3" t="n">
-        <v>10320</v>
+        <v>12013</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2631</v>
+        <v>2844</v>
       </c>
       <c r="C4" t="n">
-        <v>6951</v>
+        <v>4718</v>
       </c>
       <c r="D4" t="n">
-        <v>9913</v>
+        <v>11380</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2420</v>
+        <v>2578</v>
       </c>
       <c r="C5" t="n">
-        <v>9877</v>
+        <v>5577</v>
       </c>
       <c r="D5" t="n">
-        <v>5362</v>
+        <v>6596</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1456</v>
+        <v>1649</v>
       </c>
       <c r="C6" t="n">
-        <v>9686</v>
+        <v>6333</v>
       </c>
       <c r="D6" t="n">
-        <v>2054</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>479</v>
+        <v>614</v>
       </c>
       <c r="C7" t="n">
-        <v>6606</v>
+        <v>5080</v>
       </c>
       <c r="D7" t="n">
-        <v>800</v>
+        <v>887</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="C8" t="n">
-        <v>3560</v>
+        <v>2797</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>1272</v>
+        <v>1126</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6256</v>
+        <v>5180</v>
       </c>
       <c r="C2" t="n">
-        <v>14427</v>
+        <v>6827</v>
       </c>
       <c r="D2" t="n">
-        <v>13827</v>
+        <v>6295</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2538</v>
+        <v>3760</v>
       </c>
       <c r="C2" t="n">
-        <v>9698</v>
+        <v>7535</v>
       </c>
       <c r="D2" t="n">
-        <v>7290</v>
+        <v>9583</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3036</v>
+        <v>3735</v>
       </c>
       <c r="C3" t="n">
-        <v>7141</v>
+        <v>6683</v>
       </c>
       <c r="D3" t="n">
-        <v>11133</v>
+        <v>13130</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3581</v>
+        <v>3837</v>
       </c>
       <c r="C4" t="n">
-        <v>10237</v>
+        <v>6660</v>
       </c>
       <c r="D4" t="n">
-        <v>10093</v>
+        <v>11679</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1345</v>
+        <v>1618</v>
       </c>
       <c r="C5" t="n">
-        <v>13947</v>
+        <v>8597</v>
       </c>
       <c r="D5" t="n">
-        <v>4835</v>
+        <v>6045</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>442</v>
+        <v>567</v>
       </c>
       <c r="C6" t="n">
-        <v>8087</v>
+        <v>6281</v>
       </c>
       <c r="D6" t="n">
-        <v>1676</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>3488</v>
+        <v>2741</v>
       </c>
       <c r="D7" t="n">
-        <v>500</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>1246</v>
+        <v>1103</v>
       </c>
       <c r="D8" t="n">
-        <v>288</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="D9" t="n">
-        <v>176</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7478</v>
+        <v>7441</v>
       </c>
       <c r="C2" t="n">
-        <v>9978</v>
+        <v>3210</v>
       </c>
       <c r="D2" t="n">
-        <v>14511</v>
+        <v>8062</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2658</v>
+        <v>2201</v>
       </c>
       <c r="C3" t="n">
-        <v>7271</v>
+        <v>3495</v>
       </c>
       <c r="D3" t="n">
-        <v>2962</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5571</v>
+        <v>5532</v>
       </c>
       <c r="C2" t="n">
-        <v>5270</v>
+        <v>4481</v>
       </c>
       <c r="D2" t="n">
-        <v>19148</v>
+        <v>17523</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4160</v>
+        <v>3954</v>
       </c>
       <c r="C3" t="n">
-        <v>7591</v>
+        <v>2867</v>
       </c>
       <c r="D3" t="n">
-        <v>4684</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1189</v>
+        <v>990</v>
       </c>
       <c r="C4" t="n">
-        <v>4303</v>
+        <v>2124</v>
       </c>
       <c r="D4" t="n">
-        <v>1778</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6031</v>
+        <v>4688</v>
       </c>
       <c r="C2" t="n">
-        <v>9267</v>
+        <v>3551</v>
       </c>
       <c r="D2" t="n">
-        <v>18447</v>
+        <v>20612</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3982</v>
+        <v>3886</v>
       </c>
       <c r="C3" t="n">
-        <v>5505</v>
+        <v>3243</v>
       </c>
       <c r="D3" t="n">
-        <v>6660</v>
+        <v>4831</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2238</v>
+        <v>2089</v>
       </c>
       <c r="C4" t="n">
-        <v>6044</v>
+        <v>2480</v>
       </c>
       <c r="D4" t="n">
-        <v>2281</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>540</v>
+        <v>467</v>
       </c>
       <c r="C5" t="n">
-        <v>2412</v>
+        <v>1275</v>
       </c>
       <c r="D5" t="n">
-        <v>1267</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5361,7 +5361,7 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5403,10 +5403,10 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7023</v>
+        <v>5121</v>
       </c>
       <c r="C2" t="n">
-        <v>6719</v>
+        <v>10020</v>
       </c>
       <c r="D2" t="n">
-        <v>22927</v>
+        <v>27254</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4085</v>
+        <v>3517</v>
       </c>
       <c r="C3" t="n">
-        <v>6455</v>
+        <v>2957</v>
       </c>
       <c r="D3" t="n">
-        <v>7982</v>
+        <v>6889</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2594</v>
+        <v>2517</v>
       </c>
       <c r="C4" t="n">
-        <v>5633</v>
+        <v>2845</v>
       </c>
       <c r="D4" t="n">
-        <v>3010</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1123</v>
+        <v>1060</v>
       </c>
       <c r="C5" t="n">
-        <v>4209</v>
+        <v>1884</v>
       </c>
       <c r="D5" t="n">
-        <v>1403</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>294</v>
+        <v>266</v>
       </c>
       <c r="C6" t="n">
-        <v>1330</v>
+        <v>791</v>
       </c>
       <c r="D6" t="n">
-        <v>936</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
         <v>149</v>
@@ -5633,7 +5633,7 @@
         <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5714,10 +5714,10 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6937</v>
+        <v>5467</v>
       </c>
       <c r="C2" t="n">
-        <v>5600</v>
+        <v>6514</v>
       </c>
       <c r="D2" t="n">
-        <v>26333</v>
+        <v>32765</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3974</v>
+        <v>3141</v>
       </c>
       <c r="C3" t="n">
-        <v>5402</v>
+        <v>5432</v>
       </c>
       <c r="D3" t="n">
-        <v>9007</v>
+        <v>8936</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2058</v>
+        <v>1885</v>
       </c>
       <c r="C4" t="n">
-        <v>4917</v>
+        <v>2384</v>
       </c>
       <c r="D4" t="n">
-        <v>3265</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>950</v>
+        <v>928</v>
       </c>
       <c r="C5" t="n">
-        <v>3593</v>
+        <v>1734</v>
       </c>
       <c r="D5" t="n">
-        <v>1326</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="C6" t="n">
-        <v>1825</v>
+        <v>912</v>
       </c>
       <c r="D6" t="n">
-        <v>762</v>
+        <v>753</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>525</v>
+        <v>365</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>116</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5687</v>
+        <v>5464</v>
       </c>
       <c r="C2" t="n">
-        <v>5847</v>
+        <v>4404</v>
       </c>
       <c r="D2" t="n">
-        <v>19892</v>
+        <v>28189</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4489</v>
+        <v>3592</v>
       </c>
       <c r="C3" t="n">
-        <v>4755</v>
+        <v>5264</v>
       </c>
       <c r="D3" t="n">
-        <v>11254</v>
+        <v>12457</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2603</v>
+        <v>2216</v>
       </c>
       <c r="C4" t="n">
-        <v>5051</v>
+        <v>4184</v>
       </c>
       <c r="D4" t="n">
-        <v>4323</v>
+        <v>3849</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1333</v>
+        <v>1263</v>
       </c>
       <c r="C5" t="n">
-        <v>4280</v>
+        <v>2091</v>
       </c>
       <c r="D5" t="n">
-        <v>1645</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="C6" t="n">
-        <v>2787</v>
+        <v>1381</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>806</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C7" t="n">
-        <v>1238</v>
+        <v>681</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>383</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
         <v>196</v>
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6266,10 +6266,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4366</v>
+        <v>4812</v>
       </c>
       <c r="C2" t="n">
-        <v>13334</v>
+        <v>6498</v>
       </c>
       <c r="D2" t="n">
-        <v>23066</v>
+        <v>23543</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4165</v>
+        <v>3715</v>
       </c>
       <c r="C3" t="n">
-        <v>4629</v>
+        <v>4135</v>
       </c>
       <c r="D3" t="n">
-        <v>11774</v>
+        <v>14077</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2995</v>
+        <v>2493</v>
       </c>
       <c r="C4" t="n">
-        <v>4783</v>
+        <v>4678</v>
       </c>
       <c r="D4" t="n">
-        <v>5414</v>
+        <v>5347</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1709</v>
+        <v>1543</v>
       </c>
       <c r="C5" t="n">
-        <v>4598</v>
+        <v>3232</v>
       </c>
       <c r="D5" t="n">
-        <v>2083</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>849</v>
+        <v>835</v>
       </c>
       <c r="C6" t="n">
-        <v>3488</v>
+        <v>1753</v>
       </c>
       <c r="D6" t="n">
-        <v>974</v>
+        <v>892</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C7" t="n">
-        <v>2026</v>
+        <v>1058</v>
       </c>
       <c r="D7" t="n">
-        <v>605</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>801</v>
+        <v>498</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>288</v>
+        <v>253</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
         <v>122</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_59_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_59_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5992</v>
+        <v>6134</v>
       </c>
       <c r="C2" t="n">
-        <v>9627</v>
+        <v>6889</v>
       </c>
       <c r="D2" t="n">
-        <v>21086</v>
+        <v>21985</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3486</v>
+        <v>3321</v>
       </c>
       <c r="C3" t="n">
-        <v>4657</v>
+        <v>2915</v>
       </c>
       <c r="D3" t="n">
-        <v>14524</v>
+        <v>16490</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2655</v>
+        <v>2764</v>
       </c>
       <c r="C4" t="n">
-        <v>4288</v>
+        <v>3337</v>
       </c>
       <c r="D4" t="n">
-        <v>6776</v>
+        <v>9292</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1754</v>
+        <v>1836</v>
       </c>
       <c r="C5" t="n">
-        <v>3883</v>
+        <v>3276</v>
       </c>
       <c r="D5" t="n">
-        <v>2352</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1074</v>
+        <v>1059</v>
       </c>
       <c r="C6" t="n">
-        <v>2486</v>
+        <v>2556</v>
       </c>
       <c r="D6" t="n">
-        <v>1039</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>509</v>
+        <v>481</v>
       </c>
       <c r="C7" t="n">
-        <v>1404</v>
+        <v>1585</v>
       </c>
       <c r="D7" t="n">
-        <v>636</v>
+        <v>682</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="C8" t="n">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>368</v>
+        <v>344</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
         <v>204</v>
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7508</v>
+        <v>8067</v>
       </c>
       <c r="C2" t="n">
-        <v>7404</v>
+        <v>10612</v>
       </c>
       <c r="D2" t="n">
-        <v>25495</v>
+        <v>29280</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3754</v>
+        <v>3702</v>
       </c>
       <c r="C3" t="n">
-        <v>6150</v>
+        <v>4181</v>
       </c>
       <c r="D3" t="n">
-        <v>14469</v>
+        <v>16129</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2589</v>
+        <v>2577</v>
       </c>
       <c r="C4" t="n">
-        <v>4383</v>
+        <v>3060</v>
       </c>
       <c r="D4" t="n">
-        <v>7908</v>
+        <v>10095</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1922</v>
+        <v>1983</v>
       </c>
       <c r="C5" t="n">
-        <v>3959</v>
+        <v>3205</v>
       </c>
       <c r="D5" t="n">
-        <v>2979</v>
+        <v>4392</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1253</v>
+        <v>1285</v>
       </c>
       <c r="C6" t="n">
-        <v>3117</v>
+        <v>2862</v>
       </c>
       <c r="D6" t="n">
-        <v>1239</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>678</v>
+        <v>651</v>
       </c>
       <c r="C7" t="n">
-        <v>1888</v>
+        <v>2006</v>
       </c>
       <c r="D7" t="n">
-        <v>692</v>
+        <v>779</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="C8" t="n">
-        <v>1050</v>
+        <v>1120</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C9" t="n">
-        <v>533</v>
+        <v>513</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
         <v>128</v>
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1321,7 +1321,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9130</v>
+        <v>9533</v>
       </c>
       <c r="C2" t="n">
-        <v>7296</v>
+        <v>16133</v>
       </c>
       <c r="D2" t="n">
-        <v>30910</v>
+        <v>29110</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4321</v>
+        <v>4440</v>
       </c>
       <c r="C3" t="n">
-        <v>5972</v>
+        <v>6117</v>
       </c>
       <c r="D3" t="n">
-        <v>14931</v>
+        <v>16754</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2646</v>
+        <v>2591</v>
       </c>
       <c r="C4" t="n">
-        <v>5047</v>
+        <v>3502</v>
       </c>
       <c r="D4" t="n">
-        <v>8599</v>
+        <v>10714</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1957</v>
+        <v>1988</v>
       </c>
       <c r="C5" t="n">
-        <v>4025</v>
+        <v>3044</v>
       </c>
       <c r="D5" t="n">
-        <v>3645</v>
+        <v>5037</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1398</v>
+        <v>1449</v>
       </c>
       <c r="C6" t="n">
-        <v>3451</v>
+        <v>2952</v>
       </c>
       <c r="D6" t="n">
-        <v>1461</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>824</v>
+        <v>812</v>
       </c>
       <c r="C7" t="n">
-        <v>2386</v>
+        <v>2365</v>
       </c>
       <c r="D7" t="n">
-        <v>765</v>
+        <v>883</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>400</v>
+        <v>371</v>
       </c>
       <c r="C8" t="n">
-        <v>1394</v>
+        <v>1464</v>
       </c>
       <c r="D8" t="n">
-        <v>479</v>
+        <v>499</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="C9" t="n">
-        <v>730</v>
+        <v>750</v>
       </c>
       <c r="D9" t="n">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="D11" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
         <v>130</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8197</v>
+        <v>8544</v>
       </c>
       <c r="C2" t="n">
-        <v>4844</v>
+        <v>10841</v>
       </c>
       <c r="D2" t="n">
-        <v>25054</v>
+        <v>23698</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5052</v>
+        <v>5082</v>
       </c>
       <c r="C3" t="n">
-        <v>8711</v>
+        <v>9315</v>
       </c>
       <c r="D3" t="n">
-        <v>16566</v>
+        <v>18861</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1808</v>
+        <v>1836</v>
       </c>
       <c r="C4" t="n">
-        <v>6722</v>
+        <v>4905</v>
       </c>
       <c r="D4" t="n">
-        <v>8180</v>
+        <v>10530</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1291</v>
+        <v>1338</v>
       </c>
       <c r="C5" t="n">
-        <v>3381</v>
+        <v>2892</v>
       </c>
       <c r="D5" t="n">
-        <v>2446</v>
+        <v>3389</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>761</v>
+        <v>750</v>
       </c>
       <c r="C6" t="n">
-        <v>2338</v>
+        <v>2317</v>
       </c>
       <c r="D6" t="n">
-        <v>749</v>
+        <v>865</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>369</v>
+        <v>342</v>
       </c>
       <c r="C7" t="n">
-        <v>1366</v>
+        <v>1434</v>
       </c>
       <c r="D7" t="n">
-        <v>469</v>
+        <v>489</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>715</v>
+        <v>735</v>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
         <v>127</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
         <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1929,7 +1929,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4935</v>
+        <v>5186</v>
       </c>
       <c r="C2" t="n">
-        <v>2874</v>
+        <v>4370</v>
       </c>
       <c r="D2" t="n">
-        <v>17348</v>
+        <v>16410</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5508</v>
+        <v>5616</v>
       </c>
       <c r="C3" t="n">
-        <v>6235</v>
+        <v>9070</v>
       </c>
       <c r="D3" t="n">
-        <v>16966</v>
+        <v>18432</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2689</v>
+        <v>2673</v>
       </c>
       <c r="C4" t="n">
-        <v>7795</v>
+        <v>7018</v>
       </c>
       <c r="D4" t="n">
-        <v>9376</v>
+        <v>11691</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1414</v>
+        <v>1469</v>
       </c>
       <c r="C5" t="n">
-        <v>4884</v>
+        <v>3820</v>
       </c>
       <c r="D5" t="n">
-        <v>3134</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>916</v>
+        <v>900</v>
       </c>
       <c r="C6" t="n">
-        <v>2827</v>
+        <v>2662</v>
       </c>
       <c r="D6" t="n">
-        <v>924</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>350</v>
+        <v>321</v>
       </c>
       <c r="C7" t="n">
-        <v>1762</v>
+        <v>1788</v>
       </c>
       <c r="D7" t="n">
-        <v>508</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>928</v>
+        <v>968</v>
       </c>
       <c r="D8" t="n">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2164,7 +2164,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
         <v>99</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2226,7 +2226,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5382</v>
+        <v>4583</v>
       </c>
       <c r="C2" t="n">
-        <v>6520</v>
+        <v>5429</v>
       </c>
       <c r="D2" t="n">
-        <v>17148</v>
+        <v>20611</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4412</v>
+        <v>4600</v>
       </c>
       <c r="C3" t="n">
-        <v>4054</v>
+        <v>6032</v>
       </c>
       <c r="D3" t="n">
-        <v>15853</v>
+        <v>16872</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3392</v>
+        <v>3376</v>
       </c>
       <c r="C4" t="n">
-        <v>6839</v>
+        <v>7896</v>
       </c>
       <c r="D4" t="n">
-        <v>10402</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1739</v>
+        <v>1766</v>
       </c>
       <c r="C5" t="n">
-        <v>6254</v>
+        <v>5275</v>
       </c>
       <c r="D5" t="n">
-        <v>4057</v>
+        <v>5328</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1042</v>
+        <v>1059</v>
       </c>
       <c r="C6" t="n">
-        <v>3746</v>
+        <v>3195</v>
       </c>
       <c r="D6" t="n">
-        <v>1251</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>514</v>
+        <v>482</v>
       </c>
       <c r="C7" t="n">
-        <v>2258</v>
+        <v>2190</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="C8" t="n">
-        <v>1288</v>
+        <v>1314</v>
       </c>
       <c r="D8" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="D10" t="n">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2475,7 +2475,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
         <v>120</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3158</v>
+        <v>2701</v>
       </c>
       <c r="C2" t="n">
-        <v>2948</v>
+        <v>2499</v>
       </c>
       <c r="D2" t="n">
-        <v>11810</v>
+        <v>14266</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4486</v>
+        <v>4470</v>
       </c>
       <c r="C3" t="n">
-        <v>4785</v>
+        <v>5631</v>
       </c>
       <c r="D3" t="n">
-        <v>15617</v>
+        <v>16885</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3759</v>
+        <v>3735</v>
       </c>
       <c r="C4" t="n">
-        <v>6390</v>
+        <v>7863</v>
       </c>
       <c r="D4" t="n">
-        <v>11108</v>
+        <v>13190</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1831</v>
+        <v>1859</v>
       </c>
       <c r="C5" t="n">
-        <v>7306</v>
+        <v>6660</v>
       </c>
       <c r="D5" t="n">
-        <v>4416</v>
+        <v>5714</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>908</v>
+        <v>885</v>
       </c>
       <c r="C6" t="n">
-        <v>4630</v>
+        <v>3943</v>
       </c>
       <c r="D6" t="n">
-        <v>1235</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C7" t="n">
-        <v>2372</v>
+        <v>2356</v>
       </c>
       <c r="D7" t="n">
-        <v>573</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1035</v>
+        <v>1019</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2772,7 +2772,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
         <v>117</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4860</v>
+        <v>3416</v>
       </c>
       <c r="C2" t="n">
-        <v>8383</v>
+        <v>2531</v>
       </c>
       <c r="D2" t="n">
-        <v>12527</v>
+        <v>17809</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3316</v>
+        <v>3192</v>
       </c>
       <c r="C3" t="n">
-        <v>3477</v>
+        <v>3722</v>
       </c>
       <c r="D3" t="n">
-        <v>14144</v>
+        <v>15394</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3584</v>
+        <v>3559</v>
       </c>
       <c r="C4" t="n">
-        <v>5532</v>
+        <v>6703</v>
       </c>
       <c r="D4" t="n">
-        <v>11506</v>
+        <v>13392</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2318</v>
+        <v>2313</v>
       </c>
       <c r="C5" t="n">
-        <v>6802</v>
+        <v>7064</v>
       </c>
       <c r="D5" t="n">
-        <v>5309</v>
+        <v>6743</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1162</v>
+        <v>1138</v>
       </c>
       <c r="C6" t="n">
-        <v>5787</v>
+        <v>5156</v>
       </c>
       <c r="D6" t="n">
-        <v>1688</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="C7" t="n">
-        <v>3346</v>
+        <v>3015</v>
       </c>
       <c r="D7" t="n">
-        <v>651</v>
+        <v>731</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>1552</v>
+        <v>1546</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>551</v>
+        <v>527</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D13" t="n">
         <v>61</v>
-      </c>
-      <c r="D13" t="n">
-        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3153</v>
+        <v>2630</v>
       </c>
       <c r="C2" t="n">
-        <v>4135</v>
+        <v>1634</v>
       </c>
       <c r="D2" t="n">
-        <v>9833</v>
+        <v>13633</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3359</v>
+        <v>2860</v>
       </c>
       <c r="C3" t="n">
-        <v>4954</v>
+        <v>2968</v>
       </c>
       <c r="D3" t="n">
-        <v>13180</v>
+        <v>14846</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3224</v>
+        <v>3177</v>
       </c>
       <c r="C4" t="n">
-        <v>4708</v>
+        <v>5526</v>
       </c>
       <c r="D4" t="n">
-        <v>11621</v>
+        <v>13382</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2574</v>
+        <v>2556</v>
       </c>
       <c r="C5" t="n">
-        <v>6446</v>
+        <v>6988</v>
       </c>
       <c r="D5" t="n">
-        <v>5963</v>
+        <v>7433</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1374</v>
+        <v>1340</v>
       </c>
       <c r="C6" t="n">
-        <v>6351</v>
+        <v>5977</v>
       </c>
       <c r="D6" t="n">
-        <v>2013</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="C7" t="n">
-        <v>4196</v>
+        <v>3766</v>
       </c>
       <c r="D7" t="n">
-        <v>732</v>
+        <v>838</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>2003</v>
+        <v>1962</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>659</v>
+        <v>616</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5318</v>
+        <v>3901</v>
       </c>
       <c r="C2" t="n">
-        <v>13454</v>
+        <v>7312</v>
       </c>
       <c r="D2" t="n">
-        <v>13021</v>
+        <v>21029</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2761</v>
+        <v>2334</v>
       </c>
       <c r="C3" t="n">
-        <v>4089</v>
+        <v>2155</v>
       </c>
       <c r="D3" t="n">
-        <v>12013</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2844</v>
+        <v>2688</v>
       </c>
       <c r="C4" t="n">
-        <v>4718</v>
+        <v>4306</v>
       </c>
       <c r="D4" t="n">
-        <v>11380</v>
+        <v>13186</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2578</v>
+        <v>2526</v>
       </c>
       <c r="C5" t="n">
-        <v>5577</v>
+        <v>6239</v>
       </c>
       <c r="D5" t="n">
-        <v>6596</v>
+        <v>7935</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1649</v>
+        <v>1634</v>
       </c>
       <c r="C6" t="n">
-        <v>6333</v>
+        <v>6323</v>
       </c>
       <c r="D6" t="n">
-        <v>2517</v>
+        <v>3121</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>614</v>
+        <v>576</v>
       </c>
       <c r="C7" t="n">
-        <v>5080</v>
+        <v>4609</v>
       </c>
       <c r="D7" t="n">
-        <v>887</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C8" t="n">
-        <v>2797</v>
+        <v>2634</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1126</v>
+        <v>1070</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>370</v>
+        <v>348</v>
       </c>
       <c r="D10" t="n">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5180</v>
+        <v>5492</v>
       </c>
       <c r="C2" t="n">
-        <v>6827</v>
+        <v>5665</v>
       </c>
       <c r="D2" t="n">
-        <v>6295</v>
+        <v>13395</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3760</v>
+        <v>2762</v>
       </c>
       <c r="C2" t="n">
-        <v>7535</v>
+        <v>4153</v>
       </c>
       <c r="D2" t="n">
-        <v>9583</v>
+        <v>15477</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3735</v>
+        <v>3210</v>
       </c>
       <c r="C3" t="n">
-        <v>6683</v>
+        <v>3537</v>
       </c>
       <c r="D3" t="n">
-        <v>13130</v>
+        <v>15431</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3837</v>
+        <v>3706</v>
       </c>
       <c r="C4" t="n">
-        <v>6660</v>
+        <v>6277</v>
       </c>
       <c r="D4" t="n">
-        <v>11679</v>
+        <v>13600</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1618</v>
+        <v>1579</v>
       </c>
       <c r="C5" t="n">
-        <v>8597</v>
+        <v>8968</v>
       </c>
       <c r="D5" t="n">
-        <v>6045</v>
+        <v>7318</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>567</v>
+        <v>532</v>
       </c>
       <c r="C6" t="n">
-        <v>6281</v>
+        <v>5818</v>
       </c>
       <c r="D6" t="n">
-        <v>1980</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C7" t="n">
-        <v>2741</v>
+        <v>2581</v>
       </c>
       <c r="D7" t="n">
-        <v>573</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1103</v>
+        <v>1048</v>
       </c>
       <c r="D8" t="n">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="D9" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D11" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7441</v>
+        <v>6533</v>
       </c>
       <c r="C2" t="n">
-        <v>3210</v>
+        <v>6140</v>
       </c>
       <c r="D2" t="n">
-        <v>8062</v>
+        <v>29293</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2201</v>
+        <v>2334</v>
       </c>
       <c r="C3" t="n">
-        <v>3495</v>
+        <v>2855</v>
       </c>
       <c r="D3" t="n">
-        <v>1696</v>
+        <v>2889</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5532</v>
+        <v>5455</v>
       </c>
       <c r="C2" t="n">
-        <v>4481</v>
+        <v>4315</v>
       </c>
       <c r="D2" t="n">
-        <v>17523</v>
+        <v>23725</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3954</v>
+        <v>3639</v>
       </c>
       <c r="C3" t="n">
-        <v>2867</v>
+        <v>4065</v>
       </c>
       <c r="D3" t="n">
-        <v>2640</v>
+        <v>7112</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>990</v>
+        <v>1048</v>
       </c>
       <c r="C4" t="n">
-        <v>2124</v>
+        <v>1717</v>
       </c>
       <c r="D4" t="n">
-        <v>1523</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4688</v>
+        <v>5535</v>
       </c>
       <c r="C2" t="n">
-        <v>3551</v>
+        <v>7077</v>
       </c>
       <c r="D2" t="n">
-        <v>20612</v>
+        <v>33402</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3886</v>
+        <v>3719</v>
       </c>
       <c r="C3" t="n">
-        <v>3243</v>
+        <v>3636</v>
       </c>
       <c r="D3" t="n">
-        <v>4831</v>
+        <v>9258</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2089</v>
+        <v>1992</v>
       </c>
       <c r="C4" t="n">
-        <v>2480</v>
+        <v>3011</v>
       </c>
       <c r="D4" t="n">
-        <v>1691</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="C5" t="n">
-        <v>1275</v>
+        <v>1035</v>
       </c>
       <c r="D5" t="n">
-        <v>1200</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5361,7 +5361,7 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5121</v>
+        <v>5412</v>
       </c>
       <c r="C2" t="n">
-        <v>10020</v>
+        <v>4169</v>
       </c>
       <c r="D2" t="n">
-        <v>27254</v>
+        <v>35918</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3517</v>
+        <v>3792</v>
       </c>
       <c r="C3" t="n">
-        <v>2957</v>
+        <v>4706</v>
       </c>
       <c r="D3" t="n">
-        <v>6889</v>
+        <v>12276</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2517</v>
+        <v>2391</v>
       </c>
       <c r="C4" t="n">
-        <v>2845</v>
+        <v>3284</v>
       </c>
       <c r="D4" t="n">
-        <v>2196</v>
+        <v>3842</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1060</v>
+        <v>1013</v>
       </c>
       <c r="C5" t="n">
-        <v>1884</v>
+        <v>2037</v>
       </c>
       <c r="D5" t="n">
-        <v>1253</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="C6" t="n">
-        <v>791</v>
+        <v>662</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>955</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5467</v>
+        <v>6351</v>
       </c>
       <c r="C2" t="n">
-        <v>6514</v>
+        <v>5326</v>
       </c>
       <c r="D2" t="n">
-        <v>32765</v>
+        <v>30698</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3141</v>
+        <v>3332</v>
       </c>
       <c r="C3" t="n">
-        <v>5432</v>
+        <v>3630</v>
       </c>
       <c r="D3" t="n">
-        <v>8936</v>
+        <v>14116</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1885</v>
+        <v>1918</v>
       </c>
       <c r="C4" t="n">
-        <v>2384</v>
+        <v>3332</v>
       </c>
       <c r="D4" t="n">
-        <v>2587</v>
+        <v>4593</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>928</v>
+        <v>876</v>
       </c>
       <c r="C5" t="n">
-        <v>1734</v>
+        <v>1945</v>
       </c>
       <c r="D5" t="n">
-        <v>1124</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="C6" t="n">
         <v>912</v>
       </c>
       <c r="D6" t="n">
-        <v>753</v>
+        <v>792</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>365</v>
+        <v>322</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5843,7 +5843,7 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
         <v>360</v>
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
         <v>193</v>
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5464</v>
+        <v>5140</v>
       </c>
       <c r="C2" t="n">
-        <v>4404</v>
+        <v>3434</v>
       </c>
       <c r="D2" t="n">
-        <v>28189</v>
+        <v>27411</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3592</v>
+        <v>4027</v>
       </c>
       <c r="C3" t="n">
-        <v>5264</v>
+        <v>3973</v>
       </c>
       <c r="D3" t="n">
-        <v>12457</v>
+        <v>15862</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2216</v>
+        <v>2305</v>
       </c>
       <c r="C4" t="n">
-        <v>4184</v>
+        <v>3442</v>
       </c>
       <c r="D4" t="n">
-        <v>3849</v>
+        <v>6329</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1263</v>
+        <v>1246</v>
       </c>
       <c r="C5" t="n">
-        <v>2091</v>
+        <v>2716</v>
       </c>
       <c r="D5" t="n">
-        <v>1384</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>576</v>
+        <v>541</v>
       </c>
       <c r="C6" t="n">
-        <v>1381</v>
+        <v>1485</v>
       </c>
       <c r="D6" t="n">
-        <v>806</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C7" t="n">
-        <v>681</v>
+        <v>648</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="D8" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6185,7 +6185,7 @@
         <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4812</v>
+        <v>4320</v>
       </c>
       <c r="C2" t="n">
-        <v>6498</v>
+        <v>3501</v>
       </c>
       <c r="D2" t="n">
-        <v>23543</v>
+        <v>23735</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3715</v>
+        <v>3764</v>
       </c>
       <c r="C3" t="n">
-        <v>4135</v>
+        <v>3184</v>
       </c>
       <c r="D3" t="n">
-        <v>14077</v>
+        <v>16567</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2493</v>
+        <v>2702</v>
       </c>
       <c r="C4" t="n">
-        <v>4678</v>
+        <v>3671</v>
       </c>
       <c r="D4" t="n">
-        <v>5347</v>
+        <v>7966</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1543</v>
+        <v>1564</v>
       </c>
       <c r="C5" t="n">
-        <v>3232</v>
+        <v>3056</v>
       </c>
       <c r="D5" t="n">
-        <v>1815</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>835</v>
+        <v>804</v>
       </c>
       <c r="C6" t="n">
-        <v>1753</v>
+        <v>2103</v>
       </c>
       <c r="D6" t="n">
-        <v>892</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>341</v>
+        <v>319</v>
       </c>
       <c r="C7" t="n">
-        <v>1058</v>
+        <v>1090</v>
       </c>
       <c r="D7" t="n">
-        <v>600</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>66</v>
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_59_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_59_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6134</v>
+        <v>1097</v>
       </c>
       <c r="C2" t="n">
-        <v>6889</v>
+        <v>2511</v>
       </c>
       <c r="D2" t="n">
-        <v>21985</v>
+        <v>12874</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3321</v>
+        <v>1845</v>
       </c>
       <c r="C3" t="n">
-        <v>2915</v>
+        <v>7160</v>
       </c>
       <c r="D3" t="n">
-        <v>16490</v>
+        <v>11933</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2764</v>
+        <v>1355</v>
       </c>
       <c r="C4" t="n">
-        <v>3337</v>
+        <v>8072</v>
       </c>
       <c r="D4" t="n">
-        <v>9292</v>
+        <v>5505</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1836</v>
+        <v>753</v>
       </c>
       <c r="C5" t="n">
-        <v>3276</v>
+        <v>4156</v>
       </c>
       <c r="D5" t="n">
-        <v>3567</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1059</v>
+        <v>333</v>
       </c>
       <c r="C6" t="n">
-        <v>2556</v>
+        <v>1477</v>
       </c>
       <c r="D6" t="n">
-        <v>1347</v>
+        <v>749</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>481</v>
+        <v>112</v>
       </c>
       <c r="C7" t="n">
-        <v>1585</v>
+        <v>575</v>
       </c>
       <c r="D7" t="n">
-        <v>682</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>178</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>754</v>
+        <v>340</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>344</v>
+        <v>291</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8067</v>
+        <v>1381</v>
       </c>
       <c r="C2" t="n">
-        <v>10612</v>
+        <v>10254</v>
       </c>
       <c r="D2" t="n">
-        <v>29280</v>
+        <v>15349</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3702</v>
+        <v>1254</v>
       </c>
       <c r="C3" t="n">
-        <v>4181</v>
+        <v>4072</v>
       </c>
       <c r="D3" t="n">
-        <v>16129</v>
+        <v>11224</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2577</v>
+        <v>1385</v>
       </c>
       <c r="C4" t="n">
-        <v>3060</v>
+        <v>7396</v>
       </c>
       <c r="D4" t="n">
-        <v>10095</v>
+        <v>6571</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1983</v>
+        <v>918</v>
       </c>
       <c r="C5" t="n">
-        <v>3205</v>
+        <v>6214</v>
       </c>
       <c r="D5" t="n">
-        <v>4392</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1285</v>
+        <v>479</v>
       </c>
       <c r="C6" t="n">
-        <v>2862</v>
+        <v>2838</v>
       </c>
       <c r="D6" t="n">
-        <v>1656</v>
+        <v>926</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>651</v>
+        <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>2006</v>
+        <v>1022</v>
       </c>
       <c r="D7" t="n">
-        <v>779</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>1120</v>
+        <v>451</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>513</v>
+        <v>317</v>
       </c>
       <c r="D9" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9533</v>
+        <v>724</v>
       </c>
       <c r="C2" t="n">
-        <v>16133</v>
+        <v>4136</v>
       </c>
       <c r="D2" t="n">
-        <v>29110</v>
+        <v>10339</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4440</v>
+        <v>1241</v>
       </c>
       <c r="C3" t="n">
-        <v>6117</v>
+        <v>6368</v>
       </c>
       <c r="D3" t="n">
-        <v>16754</v>
+        <v>11446</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2591</v>
+        <v>1512</v>
       </c>
       <c r="C4" t="n">
-        <v>3502</v>
+        <v>6682</v>
       </c>
       <c r="D4" t="n">
-        <v>10714</v>
+        <v>7222</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1988</v>
+        <v>955</v>
       </c>
       <c r="C5" t="n">
-        <v>3044</v>
+        <v>7308</v>
       </c>
       <c r="D5" t="n">
-        <v>5037</v>
+        <v>2878</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1449</v>
+        <v>384</v>
       </c>
       <c r="C6" t="n">
-        <v>2952</v>
+        <v>3757</v>
       </c>
       <c r="D6" t="n">
-        <v>2028</v>
+        <v>944</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>812</v>
+        <v>77</v>
       </c>
       <c r="C7" t="n">
-        <v>2365</v>
+        <v>1019</v>
       </c>
       <c r="D7" t="n">
-        <v>883</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>371</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1464</v>
+        <v>474</v>
       </c>
       <c r="D8" t="n">
-        <v>499</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>144</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>750</v>
+        <v>244</v>
       </c>
       <c r="D9" t="n">
-        <v>335</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>355</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>209</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8544</v>
+        <v>757</v>
       </c>
       <c r="C2" t="n">
-        <v>10841</v>
+        <v>6210</v>
       </c>
       <c r="D2" t="n">
-        <v>23698</v>
+        <v>8519</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5082</v>
+        <v>853</v>
       </c>
       <c r="C3" t="n">
-        <v>9315</v>
+        <v>4575</v>
       </c>
       <c r="D3" t="n">
-        <v>18861</v>
+        <v>10471</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1836</v>
+        <v>1235</v>
       </c>
       <c r="C4" t="n">
-        <v>4905</v>
+        <v>6438</v>
       </c>
       <c r="D4" t="n">
-        <v>10530</v>
+        <v>7772</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1338</v>
+        <v>1084</v>
       </c>
       <c r="C5" t="n">
-        <v>2892</v>
+        <v>6907</v>
       </c>
       <c r="D5" t="n">
-        <v>3389</v>
+        <v>3568</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>750</v>
+        <v>567</v>
       </c>
       <c r="C6" t="n">
-        <v>2317</v>
+        <v>5496</v>
       </c>
       <c r="D6" t="n">
-        <v>865</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>342</v>
+        <v>166</v>
       </c>
       <c r="C7" t="n">
-        <v>1434</v>
+        <v>2272</v>
       </c>
       <c r="D7" t="n">
-        <v>489</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>735</v>
+        <v>707</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5186</v>
+        <v>385</v>
       </c>
       <c r="C2" t="n">
-        <v>4370</v>
+        <v>3793</v>
       </c>
       <c r="D2" t="n">
-        <v>16410</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5616</v>
+        <v>713</v>
       </c>
       <c r="C3" t="n">
-        <v>9070</v>
+        <v>4823</v>
       </c>
       <c r="D3" t="n">
-        <v>18432</v>
+        <v>9602</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2673</v>
+        <v>1019</v>
       </c>
       <c r="C4" t="n">
-        <v>7018</v>
+        <v>5613</v>
       </c>
       <c r="D4" t="n">
-        <v>11691</v>
+        <v>8024</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1469</v>
+        <v>1115</v>
       </c>
       <c r="C5" t="n">
-        <v>3820</v>
+        <v>6830</v>
       </c>
       <c r="D5" t="n">
-        <v>4242</v>
+        <v>4093</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>900</v>
+        <v>682</v>
       </c>
       <c r="C6" t="n">
-        <v>2662</v>
+        <v>6236</v>
       </c>
       <c r="D6" t="n">
-        <v>1122</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>321</v>
+        <v>186</v>
       </c>
       <c r="C7" t="n">
-        <v>1788</v>
+        <v>3406</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>968</v>
+        <v>1113</v>
       </c>
       <c r="D8" t="n">
-        <v>342</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>399</v>
+        <v>434</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4583</v>
+        <v>1232</v>
       </c>
       <c r="C2" t="n">
-        <v>5429</v>
+        <v>6066</v>
       </c>
       <c r="D2" t="n">
-        <v>20611</v>
+        <v>13777</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4600</v>
+        <v>487</v>
       </c>
       <c r="C3" t="n">
-        <v>6032</v>
+        <v>3816</v>
       </c>
       <c r="D3" t="n">
-        <v>16872</v>
+        <v>8555</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3376</v>
+        <v>778</v>
       </c>
       <c r="C4" t="n">
-        <v>7896</v>
+        <v>5109</v>
       </c>
       <c r="D4" t="n">
-        <v>12500</v>
+        <v>8037</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1766</v>
+        <v>997</v>
       </c>
       <c r="C5" t="n">
-        <v>5275</v>
+        <v>6181</v>
       </c>
       <c r="D5" t="n">
-        <v>5328</v>
+        <v>4572</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1059</v>
+        <v>793</v>
       </c>
       <c r="C6" t="n">
-        <v>3195</v>
+        <v>6438</v>
       </c>
       <c r="D6" t="n">
-        <v>1586</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>482</v>
+        <v>328</v>
       </c>
       <c r="C7" t="n">
-        <v>2190</v>
+        <v>4658</v>
       </c>
       <c r="D7" t="n">
-        <v>618</v>
+        <v>774</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>166</v>
+        <v>88</v>
       </c>
       <c r="C8" t="n">
-        <v>1314</v>
+        <v>2044</v>
       </c>
       <c r="D8" t="n">
-        <v>368</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>620</v>
+        <v>690</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2701</v>
+        <v>827</v>
       </c>
       <c r="C2" t="n">
-        <v>2499</v>
+        <v>3154</v>
       </c>
       <c r="D2" t="n">
-        <v>14266</v>
+        <v>9919</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4470</v>
+        <v>784</v>
       </c>
       <c r="C3" t="n">
-        <v>5631</v>
+        <v>4739</v>
       </c>
       <c r="D3" t="n">
-        <v>16885</v>
+        <v>9618</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3735</v>
+        <v>1298</v>
       </c>
       <c r="C4" t="n">
-        <v>7863</v>
+        <v>7070</v>
       </c>
       <c r="D4" t="n">
-        <v>13190</v>
+        <v>8421</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1859</v>
+        <v>806</v>
       </c>
       <c r="C5" t="n">
-        <v>6660</v>
+        <v>9059</v>
       </c>
       <c r="D5" t="n">
-        <v>5714</v>
+        <v>4249</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>885</v>
+        <v>303</v>
       </c>
       <c r="C6" t="n">
-        <v>3943</v>
+        <v>6205</v>
       </c>
       <c r="D6" t="n">
-        <v>1528</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="C7" t="n">
-        <v>2356</v>
+        <v>2003</v>
       </c>
       <c r="D7" t="n">
-        <v>615</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>1019</v>
+        <v>676</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3416</v>
+        <v>388</v>
       </c>
       <c r="C2" t="n">
-        <v>2531</v>
+        <v>2812</v>
       </c>
       <c r="D2" t="n">
-        <v>17809</v>
+        <v>6743</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3192</v>
+        <v>679</v>
       </c>
       <c r="C3" t="n">
-        <v>3722</v>
+        <v>3514</v>
       </c>
       <c r="D3" t="n">
-        <v>15394</v>
+        <v>8971</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3559</v>
+        <v>884</v>
       </c>
       <c r="C4" t="n">
-        <v>6703</v>
+        <v>5514</v>
       </c>
       <c r="D4" t="n">
-        <v>13392</v>
+        <v>8030</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2313</v>
+        <v>732</v>
       </c>
       <c r="C5" t="n">
-        <v>7064</v>
+        <v>7196</v>
       </c>
       <c r="D5" t="n">
-        <v>6743</v>
+        <v>4328</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1138</v>
+        <v>295</v>
       </c>
       <c r="C6" t="n">
-        <v>5156</v>
+        <v>6162</v>
       </c>
       <c r="D6" t="n">
-        <v>2070</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>339</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>3015</v>
+        <v>2722</v>
       </c>
       <c r="D7" t="n">
-        <v>731</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>1546</v>
+        <v>774</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>527</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>132</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2630</v>
+        <v>445</v>
       </c>
       <c r="C2" t="n">
-        <v>1634</v>
+        <v>5486</v>
       </c>
       <c r="D2" t="n">
-        <v>13633</v>
+        <v>10571</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2860</v>
+        <v>452</v>
       </c>
       <c r="C3" t="n">
-        <v>2968</v>
+        <v>2710</v>
       </c>
       <c r="D3" t="n">
-        <v>14846</v>
+        <v>7968</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3177</v>
+        <v>684</v>
       </c>
       <c r="C4" t="n">
-        <v>5526</v>
+        <v>4319</v>
       </c>
       <c r="D4" t="n">
-        <v>13382</v>
+        <v>7966</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2556</v>
+        <v>731</v>
       </c>
       <c r="C5" t="n">
-        <v>6988</v>
+        <v>6142</v>
       </c>
       <c r="D5" t="n">
-        <v>7433</v>
+        <v>4871</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1340</v>
+        <v>454</v>
       </c>
       <c r="C6" t="n">
-        <v>5977</v>
+        <v>6689</v>
       </c>
       <c r="D6" t="n">
-        <v>2489</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>318</v>
+        <v>150</v>
       </c>
       <c r="C7" t="n">
-        <v>3766</v>
+        <v>4440</v>
       </c>
       <c r="D7" t="n">
-        <v>838</v>
+        <v>758</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>1962</v>
+        <v>1716</v>
       </c>
       <c r="D8" t="n">
-        <v>422</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>616</v>
+        <v>504</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3901</v>
+        <v>1032</v>
       </c>
       <c r="C2" t="n">
-        <v>7312</v>
+        <v>11100</v>
       </c>
       <c r="D2" t="n">
-        <v>21029</v>
+        <v>11854</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2334</v>
+        <v>372</v>
       </c>
       <c r="C3" t="n">
-        <v>2155</v>
+        <v>3566</v>
       </c>
       <c r="D3" t="n">
-        <v>13750</v>
+        <v>7794</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2688</v>
+        <v>505</v>
       </c>
       <c r="C4" t="n">
-        <v>4306</v>
+        <v>3395</v>
       </c>
       <c r="D4" t="n">
-        <v>13186</v>
+        <v>7647</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2526</v>
+        <v>649</v>
       </c>
       <c r="C5" t="n">
-        <v>6239</v>
+        <v>5104</v>
       </c>
       <c r="D5" t="n">
-        <v>7935</v>
+        <v>5257</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1634</v>
+        <v>532</v>
       </c>
       <c r="C6" t="n">
-        <v>6323</v>
+        <v>6356</v>
       </c>
       <c r="D6" t="n">
-        <v>3121</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>576</v>
+        <v>250</v>
       </c>
       <c r="C7" t="n">
-        <v>4609</v>
+        <v>5496</v>
       </c>
       <c r="D7" t="n">
-        <v>1039</v>
+        <v>956</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>2634</v>
+        <v>2943</v>
       </c>
       <c r="D8" t="n">
-        <v>466</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>1070</v>
+        <v>1026</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>348</v>
+        <v>319</v>
       </c>
       <c r="D10" t="n">
-        <v>188</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5492</v>
+        <v>6073</v>
       </c>
       <c r="C2" t="n">
-        <v>5665</v>
+        <v>5823</v>
       </c>
       <c r="D2" t="n">
-        <v>13395</v>
+        <v>6329</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2762</v>
+        <v>1590</v>
       </c>
       <c r="C2" t="n">
-        <v>4153</v>
+        <v>11726</v>
       </c>
       <c r="D2" t="n">
-        <v>15477</v>
+        <v>12534</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3210</v>
+        <v>525</v>
       </c>
       <c r="C3" t="n">
-        <v>3537</v>
+        <v>6097</v>
       </c>
       <c r="D3" t="n">
-        <v>15431</v>
+        <v>7822</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3706</v>
+        <v>392</v>
       </c>
       <c r="C4" t="n">
-        <v>6277</v>
+        <v>3404</v>
       </c>
       <c r="D4" t="n">
-        <v>13600</v>
+        <v>7438</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1579</v>
+        <v>539</v>
       </c>
       <c r="C5" t="n">
-        <v>8968</v>
+        <v>4226</v>
       </c>
       <c r="D5" t="n">
-        <v>7318</v>
+        <v>5464</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="C6" t="n">
-        <v>5818</v>
+        <v>5693</v>
       </c>
       <c r="D6" t="n">
-        <v>2415</v>
+        <v>2872</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>109</v>
+        <v>327</v>
       </c>
       <c r="C7" t="n">
-        <v>2581</v>
+        <v>5864</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>1048</v>
+        <v>3963</v>
       </c>
       <c r="D8" t="n">
-        <v>299</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>341</v>
+        <v>1795</v>
       </c>
       <c r="D9" t="n">
-        <v>184</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>159</v>
+        <v>589</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>92</v>
+        <v>200</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6533</v>
+        <v>4349</v>
       </c>
       <c r="C2" t="n">
-        <v>6140</v>
+        <v>7297</v>
       </c>
       <c r="D2" t="n">
-        <v>29293</v>
+        <v>22972</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2334</v>
+        <v>2005</v>
       </c>
       <c r="C3" t="n">
-        <v>2855</v>
+        <v>2299</v>
       </c>
       <c r="D3" t="n">
-        <v>2889</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5455</v>
+        <v>2469</v>
       </c>
       <c r="C2" t="n">
-        <v>4315</v>
+        <v>6789</v>
       </c>
       <c r="D2" t="n">
-        <v>23725</v>
+        <v>19221</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3639</v>
+        <v>2664</v>
       </c>
       <c r="C3" t="n">
-        <v>4065</v>
+        <v>4566</v>
       </c>
       <c r="D3" t="n">
-        <v>7112</v>
+        <v>5156</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1048</v>
+        <v>951</v>
       </c>
       <c r="C4" t="n">
-        <v>1717</v>
+        <v>1482</v>
       </c>
       <c r="D4" t="n">
-        <v>1763</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5535</v>
+        <v>2895</v>
       </c>
       <c r="C2" t="n">
-        <v>7077</v>
+        <v>5006</v>
       </c>
       <c r="D2" t="n">
-        <v>33402</v>
+        <v>15292</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3719</v>
+        <v>2116</v>
       </c>
       <c r="C3" t="n">
-        <v>3636</v>
+        <v>5043</v>
       </c>
       <c r="D3" t="n">
-        <v>9258</v>
+        <v>7139</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1992</v>
+        <v>1585</v>
       </c>
       <c r="C4" t="n">
-        <v>3011</v>
+        <v>3316</v>
       </c>
       <c r="D4" t="n">
-        <v>2736</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>482</v>
+        <v>452</v>
       </c>
       <c r="C5" t="n">
-        <v>1035</v>
+        <v>948</v>
       </c>
       <c r="D5" t="n">
-        <v>1253</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>403</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>218</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5412</v>
+        <v>1907</v>
       </c>
       <c r="C2" t="n">
-        <v>4169</v>
+        <v>6314</v>
       </c>
       <c r="D2" t="n">
-        <v>35918</v>
+        <v>17584</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3792</v>
+        <v>2059</v>
       </c>
       <c r="C3" t="n">
-        <v>4706</v>
+        <v>4339</v>
       </c>
       <c r="D3" t="n">
-        <v>12276</v>
+        <v>7929</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2391</v>
+        <v>1603</v>
       </c>
       <c r="C4" t="n">
-        <v>3284</v>
+        <v>4241</v>
       </c>
       <c r="D4" t="n">
-        <v>3842</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1013</v>
+        <v>869</v>
       </c>
       <c r="C5" t="n">
-        <v>2037</v>
+        <v>2246</v>
       </c>
       <c r="D5" t="n">
-        <v>1459</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="C6" t="n">
-        <v>662</v>
+        <v>626</v>
       </c>
       <c r="D6" t="n">
-        <v>955</v>
+        <v>836</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>293</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>252</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>195</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6351</v>
+        <v>1732</v>
       </c>
       <c r="C2" t="n">
-        <v>5326</v>
+        <v>9844</v>
       </c>
       <c r="D2" t="n">
-        <v>30698</v>
+        <v>22642</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3332</v>
+        <v>1644</v>
       </c>
       <c r="C3" t="n">
-        <v>3630</v>
+        <v>4670</v>
       </c>
       <c r="D3" t="n">
-        <v>14116</v>
+        <v>8838</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1918</v>
+        <v>1579</v>
       </c>
       <c r="C4" t="n">
-        <v>3332</v>
+        <v>4206</v>
       </c>
       <c r="D4" t="n">
-        <v>4593</v>
+        <v>3779</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>876</v>
+        <v>1077</v>
       </c>
       <c r="C5" t="n">
-        <v>1945</v>
+        <v>3252</v>
       </c>
       <c r="D5" t="n">
-        <v>1467</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>302</v>
+        <v>486</v>
       </c>
       <c r="C6" t="n">
-        <v>912</v>
+        <v>1437</v>
       </c>
       <c r="D6" t="n">
-        <v>792</v>
+        <v>893</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>322</v>
+        <v>462</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5140</v>
+        <v>2240</v>
       </c>
       <c r="C2" t="n">
-        <v>3434</v>
+        <v>10651</v>
       </c>
       <c r="D2" t="n">
-        <v>27411</v>
+        <v>24031</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4027</v>
+        <v>1393</v>
       </c>
       <c r="C3" t="n">
-        <v>3973</v>
+        <v>6314</v>
       </c>
       <c r="D3" t="n">
-        <v>15862</v>
+        <v>10217</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2305</v>
+        <v>1397</v>
       </c>
       <c r="C4" t="n">
-        <v>3442</v>
+        <v>4359</v>
       </c>
       <c r="D4" t="n">
-        <v>6329</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1246</v>
+        <v>1155</v>
       </c>
       <c r="C5" t="n">
-        <v>2716</v>
+        <v>3660</v>
       </c>
       <c r="D5" t="n">
-        <v>2052</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>541</v>
+        <v>687</v>
       </c>
       <c r="C6" t="n">
-        <v>1485</v>
+        <v>2279</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>983</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>179</v>
+        <v>268</v>
       </c>
       <c r="C7" t="n">
-        <v>648</v>
+        <v>930</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>276</v>
+        <v>375</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4320</v>
+        <v>2005</v>
       </c>
       <c r="C2" t="n">
-        <v>3501</v>
+        <v>6475</v>
       </c>
       <c r="D2" t="n">
-        <v>23735</v>
+        <v>18746</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3764</v>
+        <v>2163</v>
       </c>
       <c r="C3" t="n">
-        <v>3184</v>
+        <v>9529</v>
       </c>
       <c r="D3" t="n">
-        <v>16567</v>
+        <v>11540</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2702</v>
+        <v>1067</v>
       </c>
       <c r="C4" t="n">
-        <v>3671</v>
+        <v>6275</v>
       </c>
       <c r="D4" t="n">
-        <v>7966</v>
+        <v>4303</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1564</v>
+        <v>634</v>
       </c>
       <c r="C5" t="n">
-        <v>3056</v>
+        <v>2233</v>
       </c>
       <c r="D5" t="n">
-        <v>2750</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>804</v>
+        <v>247</v>
       </c>
       <c r="C6" t="n">
-        <v>2103</v>
+        <v>911</v>
       </c>
       <c r="D6" t="n">
-        <v>1105</v>
+        <v>630</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>319</v>
+        <v>101</v>
       </c>
       <c r="C7" t="n">
-        <v>1090</v>
+        <v>367</v>
       </c>
       <c r="D7" t="n">
-        <v>606</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>465</v>
+        <v>282</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
         <v>201</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
